--- a/2022/Beirut1/Beirut1_members_final.xlsx
+++ b/2022/Beirut1/Beirut1_members_final.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
